--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D497B2A0-9030-40DF-89DE-1FA2CBD85FF4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB2BD287-9263-4BF8-B67A-69990DDB7086}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EEEBFA76-7515-4728-A415-309822D5AFBD}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A078E2A-98FB-413E-BE94-FA1453A2170F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8B6A873B-BD8A-4B6D-8C81-AD3B975B4316}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B13A2A5-E9CC-4246-86FA-30478E2E0DA5}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB2BD287-9263-4BF8-B67A-69990DDB7086}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC8A6382-4373-4BB8-8605-AB3FB420E505}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A078E2A-98FB-413E-BE94-FA1453A2170F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACB0EAFE-1DC8-4D0B-AC28-A8ABF5B6C442}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B13A2A5-E9CC-4246-86FA-30478E2E0DA5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9975488-D454-4EF6-8867-DEEEE1206C40}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC8A6382-4373-4BB8-8605-AB3FB420E505}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57899F45-338F-487F-8134-67B779FB7A78}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ACB0EAFE-1DC8-4D0B-AC28-A8ABF5B6C442}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49B33C8F-53D8-4532-96B9-95E7C954474B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9975488-D454-4EF6-8867-DEEEE1206C40}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BD88E7C-98B4-4749-A449-366F6D995095}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{57899F45-338F-487F-8134-67B779FB7A78}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5582668-03D9-4960-A7FB-61CCED277706}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{49B33C8F-53D8-4532-96B9-95E7C954474B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78245716-1D16-4251-9386-32F9EFB3BE9E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4BD88E7C-98B4-4749-A449-366F6D995095}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EEE320-2A45-4A51-B59F-8E3CAEDF267E}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5582668-03D9-4960-A7FB-61CCED277706}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB1007B3-B6FE-4BF4-A4E3-925A5C2666F9}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{78245716-1D16-4251-9386-32F9EFB3BE9E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45DA55F5-3C92-4FFD-99A5-B29E4D0D9B2F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90EEE320-2A45-4A51-B59F-8E3CAEDF267E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CE07E49-46BC-472D-A051-47A21C99D6BA}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB1007B3-B6FE-4BF4-A4E3-925A5C2666F9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{533001BB-E838-440E-BE7F-6BBE05EF5D1A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{45DA55F5-3C92-4FFD-99A5-B29E4D0D9B2F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54CAF4D5-1DC3-47DC-B63B-DA41FBA2BB5F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CE07E49-46BC-472D-A051-47A21C99D6BA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB27569-B8FB-4BAB-801F-A227ECCA49AF}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{533001BB-E838-440E-BE7F-6BBE05EF5D1A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7A944FC-55BC-420F-B9CE-E3A68D778EDE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54CAF4D5-1DC3-47DC-B63B-DA41FBA2BB5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E36361C-7EC3-459A-B068-CE16AF1DEDF0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1DB27569-B8FB-4BAB-801F-A227ECCA49AF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05A8F2F4-4DA3-4FA4-846D-D8216306F1EF}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,291 +1074,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7A944FC-55BC-420F-B9CE-E3A68D778EDE}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7E36361C-7EC3-459A-B068-CE16AF1DEDF0}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05A8F2F4-4DA3-4FA4-846D-D8216306F1EF}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,4 +1074,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26F7EF9C-29D9-472D-90ED-9772A85A247C}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{561C96F2-EF95-4BFF-B670-738AE6C59FBF}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59970D9B-ECE6-428D-B26F-C7E25710E706}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,291 +1074,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26F7EF9C-29D9-472D-90ED-9772A85A247C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{561C96F2-EF95-4BFF-B670-738AE6C59FBF}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59970D9B-ECE6-428D-B26F-C7E25710E706}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,4 +1074,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE058ABC-2F96-4593-8F73-A282AC194940}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{256F2CF8-B753-4F60-A1E0-AB5F9EC40C7C}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CCB2AFC-8452-455A-82E0-E974C65F6B5B}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AE058ABC-2F96-4593-8F73-A282AC194940}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5424C23-ED90-49CE-8359-0B6BABB5CDDA}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{256F2CF8-B753-4F60-A1E0-AB5F9EC40C7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6257262-ACA9-4998-8BF2-AA882857E5E4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4CCB2AFC-8452-455A-82E0-E974C65F6B5B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D16FD1F1-2E8D-4FB7-86A6-B62412BBB96E}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5424C23-ED90-49CE-8359-0B6BABB5CDDA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBA3072C-405D-4C28-8A37-C90A95617394}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6257262-ACA9-4998-8BF2-AA882857E5E4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF123E42-4A24-4FC0-83B8-71A6EF876791}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D16FD1F1-2E8D-4FB7-86A6-B62412BBB96E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{445AAE22-DA54-4E0B-8A90-59752B67062A}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CBA3072C-405D-4C28-8A37-C90A95617394}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52AA949A-E4B6-4740-B74F-38E88E8E2D7A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF123E42-4A24-4FC0-83B8-71A6EF876791}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E64CB67-DFEF-4CFF-B63E-E5F40A331DBB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{445AAE22-DA54-4E0B-8A90-59752B67062A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A97069AA-419D-46C5-905B-E4172FC6BB8F}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52AA949A-E4B6-4740-B74F-38E88E8E2D7A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFADC5E3-1592-47A3-A230-9B664C380E64}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E64CB67-DFEF-4CFF-B63E-E5F40A331DBB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C5C375D-A40B-4B60-9881-FD6ED2C4C318}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A97069AA-419D-46C5-905B-E4172FC6BB8F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE08169-D741-4DFF-ABFA-6A851B5190FE}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFADC5E3-1592-47A3-A230-9B664C380E64}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3072B9DF-1E97-4FE8-AABD-4031B094A37C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C5C375D-A40B-4B60-9881-FD6ED2C4C318}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{097DD82D-3F76-4D07-AD79-16458DAD667C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3EE08169-D741-4DFF-ABFA-6A851B5190FE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E98449B-121A-4D55-819C-E44B322029C0}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,291 +1074,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3072B9DF-1E97-4FE8-AABD-4031B094A37C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{097DD82D-3F76-4D07-AD79-16458DAD667C}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E98449B-121A-4D55-819C-E44B322029C0}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,4 +1074,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB9C2505-2FCC-4431-8AA8-0D7245AC82A7}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E59FA0B-0090-4F39-9BBA-EF5CC1D147F0}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3C53C5-2E42-4A93-8EBC-81673A9F4EF3}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB9C2505-2FCC-4431-8AA8-0D7245AC82A7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0549D028-5D16-4156-85E3-1ABAA5F59317}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E59FA0B-0090-4F39-9BBA-EF5CC1D147F0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F1D25C-9722-415A-B383-EE7462B8E17C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C3C53C5-2E42-4A93-8EBC-81673A9F4EF3}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85F21CF4-2499-41B9-B40B-15C13A05DD82}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0549D028-5D16-4156-85E3-1ABAA5F59317}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7756F85B-BB12-4AD0-B008-E74992567C84}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2F1D25C-9722-415A-B383-EE7462B8E17C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC552CF7-E554-4A2E-9FCA-1858899B9DC2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{85F21CF4-2499-41B9-B40B-15C13A05DD82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79505B8A-AB3C-46ED-9D74-A0A5D84DBBDF}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1352,13 +1352,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7756F85B-BB12-4AD0-B008-E74992567C84}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67F34B82-09C3-4051-80B1-4A3356F5EA4C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AC552CF7-E554-4A2E-9FCA-1858899B9DC2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA692B87-1276-430B-95CC-19E8E3AB1BF7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79505B8A-AB3C-46ED-9D74-A0A5D84DBBDF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4480088-2A76-4276-B589-D0D67E17AEF3}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,291 +1074,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
-    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67F34B82-09C3-4051-80B1-4A3356F5EA4C}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA692B87-1276-430B-95CC-19E8E3AB1BF7}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E4480088-2A76-4276-B589-D0D67E17AEF3}"/>
 </file>
--- a/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
+++ b/Nudo_etal_1995/Nudo_etal_1995_TABLE4_snapshot.xlsx
@@ -1074,4 +1074,291 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
+    <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="12" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="2a91012f-191a-4297-80da-223551dc3c4f" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="22" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="17" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="18" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="21" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ec99e049-fb75-4c8f-a4b4-b132771b9bd6}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C21C69C6-6975-4B31-9601-2073B9C4343E}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97EAE709-FBEA-4B17-A661-471EED2C8047}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F6F9C773-FD02-4974-8A95-15974DC9F399}"/>
 </file>